--- a/data/exports/channeladvisor-changes-to-review-2026-09-30.xlsx
+++ b/data/exports/channeladvisor-changes-to-review-2026-09-30.xlsx
@@ -684,9 +684,9 @@
       <c r="G7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CHECK - ChannelAdvisor changed the bed size (e.g. 6.5 ft/78" -&gt; 6.6 ft/79.4") and removed "Will not fit 2022 new body". Kept the old fitment on the site. Confirm which is right.</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -785,7 +785,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+          <t>DONE 2026-10-08 - applied to the site (years + new exclusions)</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -813,12 +813,16 @@
           <t>https://stehlenauto.com/products/2015-2026-ford-f-150-5-5-ft-bed-hidden-snap-soft-roll-up-tonneau-cover</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Y (applied)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+          <t>DONE 2026-10-08 - applied to the site (years + new exclusions)</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -846,12 +850,16 @@
           <t>https://stehlenauto.com/products/2015-2023-ford-f-150-super-duty-86-aluminum-running-boards-matte-black</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Y (applied)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+          <t>DONE 2026-10-08 - applied to the site (years + new exclusions)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -879,12 +887,16 @@
           <t>https://stehlenauto.com/products/2015-2023-ford-f-150-super-duty-86-oe-style-running-boards-matte-black</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Y (applied)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+          <t>DONE 2026-10-08 - applied to the site (years + new exclusions)</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -912,7 +924,11 @@
           <t>https://stehlenauto.com/products/2015-2023-ford-f-150-super-duty-86-oe-style-running-boards-silver</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Y (applied)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1113,9 +1129,9 @@
       <c r="G20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CHECK - ChannelAdvisor changed the bed size (e.g. 6.5 ft/78" -&gt; 6.6 ft/79.4") and removed "Will not fit 2022 new body". Kept the old fitment on the site. Confirm which is right.</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1146,9 +1162,9 @@
       <c r="G21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CHECK - ChannelAdvisor changed the bed size (e.g. 6.5 ft/78" -&gt; 6.6 ft/79.4") and removed "Will not fit 2022 new body". Kept the old fitment on the site. Confirm which is right.</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1179,9 +1195,9 @@
       <c r="G22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>CHECK - ChannelAdvisor changed the bed size (e.g. 6.5 ft/78" -&gt; 6.6 ft/79.4") and removed "Will not fit 2022 new body". Kept the old fitment on the site. Confirm which is right.</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1212,9 +1228,9 @@
       <c r="G23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CHECK - ChannelAdvisor changed the bed size (e.g. 6.5 ft/78" -&gt; 6.6 ft/79.4") and removed "Will not fit 2022 new body". Kept the old fitment on the site. Confirm which is right.</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1245,9 +1261,9 @@
       <c r="G24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>CHECK - ChannelAdvisor changed the bed size (e.g. 6.5 ft/78" -&gt; 6.6 ft/79.4") and removed "Will not fit 2022 new body". Kept the old fitment on the site. Confirm which is right.</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1280,7 +1296,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+          <t>DONE 2026-10-08 - applied to the site (years + new exclusions)</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1308,12 +1324,16 @@
           <t>https://stehlenauto.com/products/2020-chevy-silverado-gmc-sierra-2500-3500-hd-6-9-rubber-bed-mat</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Y (applied)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+          <t>DONE 2026-10-08 - applied to the site (years + new exclusions)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1341,12 +1361,16 @@
           <t>https://stehlenauto.com/products/access-truck-bed-mat-2020-chevy-silverado-gmc-sierra-2500-3500-hd-6-9</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Y (applied)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+          <t>DONE 2026-10-08 - applied to the site (years + new exclusions)</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1374,12 +1398,16 @@
           <t>https://stehlenauto.com/products/2020-chevy-silverado-gmc-sierra-2500-3500-hd-8ft-rubber-bed-mat</t>
         </is>
       </c>
-      <c r="G28" s="3" t="inlineStr"/>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Y (applied)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+          <t>DONE 2026-10-08 - applied to the site (years + new exclusions)</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1407,12 +1435,16 @@
           <t>https://stehlenauto.com/products/2020-2025-chevy-silverado-gmc-sierra-2500-3500-hd-8-bed-mat-rubber</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Y (applied)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Likely OK - newer model years of the same vehicles</t>
+          <t>DONE 2026-10-08 - applied to the site (years + new exclusions)</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1440,7 +1472,11 @@
           <t>https://stehlenauto.com/products/1997-2004-ford-f-150-f-250-styleside-6-5-ft-bed-hidden-snap-soft-roll-up-tonneau-cover</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Y (applied)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
